--- a/DesignData/Excel_Masters/CharacterLevelUpData_Master.xlsx
+++ b/DesignData/Excel_Masters/CharacterLevelUpData_Master.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17910" windowHeight="10695"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25680" windowHeight="10965"/>
   </bookViews>
   <sheets>
     <sheet name="CharacterLevelUpData" sheetId="1" r:id="rId1"/>
@@ -951,7 +951,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E60"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -1464,6 +1464,516 @@
         <v>150</v>
       </c>
     </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>31</v>
+      </c>
+      <c r="B31">
+        <v>2000</v>
+      </c>
+      <c r="C31">
+        <v>300</v>
+      </c>
+      <c r="D31">
+        <v>300</v>
+      </c>
+      <c r="E31">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>32</v>
+      </c>
+      <c r="B32">
+        <v>2000</v>
+      </c>
+      <c r="C32">
+        <v>300</v>
+      </c>
+      <c r="D32">
+        <v>300</v>
+      </c>
+      <c r="E32">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>33</v>
+      </c>
+      <c r="B33">
+        <v>2000</v>
+      </c>
+      <c r="C33">
+        <v>300</v>
+      </c>
+      <c r="D33">
+        <v>300</v>
+      </c>
+      <c r="E33">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <v>34</v>
+      </c>
+      <c r="B34">
+        <v>2000</v>
+      </c>
+      <c r="C34">
+        <v>300</v>
+      </c>
+      <c r="D34">
+        <v>300</v>
+      </c>
+      <c r="E34">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <v>35</v>
+      </c>
+      <c r="B35">
+        <v>2000</v>
+      </c>
+      <c r="C35">
+        <v>300</v>
+      </c>
+      <c r="D35">
+        <v>300</v>
+      </c>
+      <c r="E35">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <v>36</v>
+      </c>
+      <c r="B36">
+        <v>2000</v>
+      </c>
+      <c r="C36">
+        <v>300</v>
+      </c>
+      <c r="D36">
+        <v>300</v>
+      </c>
+      <c r="E36">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37">
+        <v>37</v>
+      </c>
+      <c r="B37">
+        <v>2000</v>
+      </c>
+      <c r="C37">
+        <v>300</v>
+      </c>
+      <c r="D37">
+        <v>300</v>
+      </c>
+      <c r="E37">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38">
+        <v>38</v>
+      </c>
+      <c r="B38">
+        <v>2000</v>
+      </c>
+      <c r="C38">
+        <v>300</v>
+      </c>
+      <c r="D38">
+        <v>300</v>
+      </c>
+      <c r="E38">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39">
+        <v>39</v>
+      </c>
+      <c r="B39">
+        <v>2000</v>
+      </c>
+      <c r="C39">
+        <v>300</v>
+      </c>
+      <c r="D39">
+        <v>300</v>
+      </c>
+      <c r="E39">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A40">
+        <v>40</v>
+      </c>
+      <c r="B40">
+        <v>2000</v>
+      </c>
+      <c r="C40">
+        <v>300</v>
+      </c>
+      <c r="D40">
+        <v>300</v>
+      </c>
+      <c r="E40">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A41">
+        <v>41</v>
+      </c>
+      <c r="B41">
+        <v>2000</v>
+      </c>
+      <c r="C41">
+        <v>300</v>
+      </c>
+      <c r="D41">
+        <v>300</v>
+      </c>
+      <c r="E41">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <v>42</v>
+      </c>
+      <c r="B42">
+        <v>2000</v>
+      </c>
+      <c r="C42">
+        <v>300</v>
+      </c>
+      <c r="D42">
+        <v>300</v>
+      </c>
+      <c r="E42">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A43">
+        <v>43</v>
+      </c>
+      <c r="B43">
+        <v>2000</v>
+      </c>
+      <c r="C43">
+        <v>300</v>
+      </c>
+      <c r="D43">
+        <v>300</v>
+      </c>
+      <c r="E43">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44">
+        <v>44</v>
+      </c>
+      <c r="B44">
+        <v>2000</v>
+      </c>
+      <c r="C44">
+        <v>300</v>
+      </c>
+      <c r="D44">
+        <v>300</v>
+      </c>
+      <c r="E44">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A45">
+        <v>45</v>
+      </c>
+      <c r="B45">
+        <v>2000</v>
+      </c>
+      <c r="C45">
+        <v>300</v>
+      </c>
+      <c r="D45">
+        <v>300</v>
+      </c>
+      <c r="E45">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A46">
+        <v>46</v>
+      </c>
+      <c r="B46">
+        <v>2000</v>
+      </c>
+      <c r="C46">
+        <v>300</v>
+      </c>
+      <c r="D46">
+        <v>300</v>
+      </c>
+      <c r="E46">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A47">
+        <v>47</v>
+      </c>
+      <c r="B47">
+        <v>2000</v>
+      </c>
+      <c r="C47">
+        <v>300</v>
+      </c>
+      <c r="D47">
+        <v>300</v>
+      </c>
+      <c r="E47">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A48">
+        <v>48</v>
+      </c>
+      <c r="B48">
+        <v>2000</v>
+      </c>
+      <c r="C48">
+        <v>300</v>
+      </c>
+      <c r="D48">
+        <v>300</v>
+      </c>
+      <c r="E48">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A49">
+        <v>49</v>
+      </c>
+      <c r="B49">
+        <v>2000</v>
+      </c>
+      <c r="C49">
+        <v>300</v>
+      </c>
+      <c r="D49">
+        <v>300</v>
+      </c>
+      <c r="E49">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A50">
+        <v>50</v>
+      </c>
+      <c r="B50">
+        <v>2000</v>
+      </c>
+      <c r="C50">
+        <v>300</v>
+      </c>
+      <c r="D50">
+        <v>300</v>
+      </c>
+      <c r="E50">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A51">
+        <v>51</v>
+      </c>
+      <c r="B51">
+        <v>2000</v>
+      </c>
+      <c r="C51">
+        <v>300</v>
+      </c>
+      <c r="D51">
+        <v>300</v>
+      </c>
+      <c r="E51">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A52">
+        <v>52</v>
+      </c>
+      <c r="B52">
+        <v>2000</v>
+      </c>
+      <c r="C52">
+        <v>300</v>
+      </c>
+      <c r="D52">
+        <v>300</v>
+      </c>
+      <c r="E52">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A53">
+        <v>53</v>
+      </c>
+      <c r="B53">
+        <v>2000</v>
+      </c>
+      <c r="C53">
+        <v>300</v>
+      </c>
+      <c r="D53">
+        <v>300</v>
+      </c>
+      <c r="E53">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A54">
+        <v>54</v>
+      </c>
+      <c r="B54">
+        <v>2000</v>
+      </c>
+      <c r="C54">
+        <v>300</v>
+      </c>
+      <c r="D54">
+        <v>300</v>
+      </c>
+      <c r="E54">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A55">
+        <v>55</v>
+      </c>
+      <c r="B55">
+        <v>2000</v>
+      </c>
+      <c r="C55">
+        <v>300</v>
+      </c>
+      <c r="D55">
+        <v>300</v>
+      </c>
+      <c r="E55">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <v>56</v>
+      </c>
+      <c r="B56">
+        <v>2000</v>
+      </c>
+      <c r="C56">
+        <v>300</v>
+      </c>
+      <c r="D56">
+        <v>300</v>
+      </c>
+      <c r="E56">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A57">
+        <v>57</v>
+      </c>
+      <c r="B57">
+        <v>2000</v>
+      </c>
+      <c r="C57">
+        <v>300</v>
+      </c>
+      <c r="D57">
+        <v>300</v>
+      </c>
+      <c r="E57">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A58">
+        <v>58</v>
+      </c>
+      <c r="B58">
+        <v>2000</v>
+      </c>
+      <c r="C58">
+        <v>300</v>
+      </c>
+      <c r="D58">
+        <v>300</v>
+      </c>
+      <c r="E58">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A59">
+        <v>59</v>
+      </c>
+      <c r="B59">
+        <v>2000</v>
+      </c>
+      <c r="C59">
+        <v>300</v>
+      </c>
+      <c r="D59">
+        <v>300</v>
+      </c>
+      <c r="E59">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A60">
+        <v>60</v>
+      </c>
+      <c r="B60">
+        <v>2000</v>
+      </c>
+      <c r="C60">
+        <v>300</v>
+      </c>
+      <c r="D60">
+        <v>300</v>
+      </c>
+      <c r="E60">
+        <v>150</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
